--- a/data/trans_orig/IP07KS_C10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C10_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de poder prestar atención en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de poder prestar atención, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21386</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15718</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27151</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18292</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13438</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22604</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21130</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39422</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32114</t>
+          <t>32754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18493</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12728</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24161</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12195</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7883</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17049</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23062</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37497</t>
+          <t>39155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21107</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15552</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26026</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14944</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10360</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19296</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35688</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>29467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>43021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10042</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5593</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15327</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7444</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16246</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>29330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6258</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5769</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5912</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6101</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4924</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5084</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13688</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19048</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6799</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>46,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10744</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6454</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15923</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>59,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6967</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10201</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5647</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,94%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4737</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1693</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5145</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37950</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26699</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>46721</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,67%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>38,46%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>17907</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33218</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>26,66%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>49,46%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47930</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>56144</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74963</t>
+          <t>66935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>24816</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16137</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>36815</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>53,04%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>47416</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>30540</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>60766</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>45,48%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>72955</t>
+          <t>48817</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103049</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6648</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2893</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5404</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>28553</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>19508</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>41298</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>32,99%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>69,83%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>18569</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>13786</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>23807</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>66,67%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>48321</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38662</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65406</t>
+          <t>61897</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>63,08%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20347</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>11737</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>29250</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>16023</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>10705</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>20577</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>57,62%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12758</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>7024</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>2894</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>12710</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -3787,107 +3787,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>9408</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>9555</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2943</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>13637</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>8852</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>19308</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>38,28%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>54,2%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>19149</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>14840</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>23398</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>63,46%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>49,18%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>25620</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>17897</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>12134</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>50,24%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>9461</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>5463</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>13664</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>31,35%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>18,1%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>45,28%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33570</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1567</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4725</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>361</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>65382</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>65382</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>65382</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>136321</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>118746</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>155353</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>44,94%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>58,8%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>95660</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>60549</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>114832</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>46,16%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>55,41%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>138597</t>
+          <t>100422</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>120069</t>
+          <t>89203</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>159894</t>
+          <t>113028</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>234257</t>
+          <t>236742</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>190071</t>
+          <t>215787</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>262495</t>
+          <t>260545</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>102338</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>83699</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>119757</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>38,73%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>45,32%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>103612</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>84146</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>144863</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>69,9%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>101378</t>
+          <t>85259</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>83641</t>
+          <t>72320</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>120535</t>
+          <t>95849</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>204990</t>
+          <t>187597</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>177135</t>
+          <t>165268</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>256106</t>
+          <t>207951</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>21499</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>14255</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>31908</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>2978</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>12635</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>31599</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>28680</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39158</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>11385</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>6185</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>11274</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5264,107 +5264,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>264228</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>264228</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>264228</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266020</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266020</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266020</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>473266</t>
+          <t>458317</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>473266</t>
+          <t>458317</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>473266</t>
+          <t>458317</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
